--- a/tame_output/ON/bt/strategyON_20231028.xlsx
+++ b/tame_output/ON/bt/strategyON_20231028.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>81.3%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.6%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.6%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.7%</t>
+          <t>132.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1763"/>
+  <dimension ref="A1:G1764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42059,7 +42059,7 @@
         <v>45225</v>
       </c>
       <c r="B1763" t="n">
-        <v>3.050333564974015</v>
+        <v>3.050895742336375</v>
       </c>
       <c r="C1763" t="n">
         <v>3.016062350193502</v>
@@ -42075,6 +42075,29 @@
       </c>
       <c r="G1763" t="n">
         <v>4.311920062562489</v>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" s="2" t="n">
+        <v>45226</v>
+      </c>
+      <c r="B1764" t="n">
+        <v>3.048350097323861</v>
+      </c>
+      <c r="C1764" t="n">
+        <v>3.030639375029551</v>
+      </c>
+      <c r="D1764" t="n">
+        <v>1.53038741157259</v>
+      </c>
+      <c r="E1764" t="n">
+        <v>3.642437915344841</v>
+      </c>
+      <c r="F1764" t="n">
+        <v>2.160879135939536</v>
+      </c>
+      <c r="G1764" t="n">
+        <v>4.327166856593275</v>
       </c>
     </row>
   </sheetData>
